--- a/employee_surveys/011_employee_onboarding_survey--employee_surveys.xlsx
+++ b/employee_surveys/011_employee_onboarding_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>employee_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>onboarding_experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>onboarding_process</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Job Role</t>
+          <t>Onboarding Process</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,69 +584,69 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page_4</t>
+          <t>job_role</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Onboarding Process</t>
+          <t>Job Role</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_5</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Job Role</t>
+          <t>Training Hours</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_6</t>
+          <t>time_to_complete</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Onboarding Experience</t>
+          <t>Days to Complete Onboarding</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,87 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_7</t>
+          <t>equipment_access</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Onboarding Process</t>
+          <t>Access to Equipment</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>onboarding_buddy</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Onboarding Buddy</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>supervisor_communication</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Supervisor Communication</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>onboarding_plan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Onboarding Plan</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -684,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -712,51 +781,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_5_choices</t>
+          <t>job_role_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1'}</t>
+          <t>data_analyst</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1', 'label': 'Option 1'}</t>
+          <t>Data Analyst</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_5_choices</t>
+          <t>job_role_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2'}</t>
+          <t>it_support</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2', 'label': 'Option 2'}</t>
+          <t>IT Support</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_5_choices</t>
+          <t>job_role_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3',_'label':_'option_3'}</t>
+          <t>marketing_manager</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 3', 'label': 'Option 3'}</t>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>onboarding_plan_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>comprehensive</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>onboarding_plan_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>onboarding_plan_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
